--- a/4.4.3 гониометр/измерения.xlsx
+++ b/4.4.3 гониометр/измерения.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\бакалавриат\4 semester (try 2)\лабы\гониометр\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\бакалавриат\4 semester (try 2)\лабы\4.4.3 гониометр\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15850" windowHeight="7260" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15850" windowHeight="7260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="параметры установки" sheetId="1" r:id="rId1"/>
     <sheet name="измерение спектра" sheetId="2" r:id="rId2"/>
-    <sheet name="оценка точности" sheetId="3" r:id="rId3"/>
+    <sheet name="плохие измерения спектра" sheetId="4" r:id="rId3"/>
+    <sheet name="оценка точности" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>начальный угол</t>
   </si>
@@ -98,6 +99,12 @@
   </si>
   <si>
     <t>ширина желтой щели 2</t>
+  </si>
+  <si>
+    <t>lambda, nm</t>
+  </si>
+  <si>
+    <t>абсолютные</t>
   </si>
 </sst>
 </file>
@@ -496,6 +503,10 @@
       <c r="D7">
         <v>28</v>
       </c>
+      <c r="E7">
+        <f>(B7-360)*3600-C7*60 -D7</f>
+        <v>-242248</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B8">
@@ -507,6 +518,16 @@
       <c r="D8">
         <v>6</v>
       </c>
+      <c r="E8">
+        <f>B8*3600+C8*60 +D8</f>
+        <v>181146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E9">
+        <f>E8-E7</f>
+        <v>423394</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -531,235 +552,193 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>308</v>
+        <v>579.1</v>
       </c>
       <c r="C2">
+        <v>308</v>
+      </c>
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>42</v>
-      </c>
-      <c r="F2">
-        <v>308</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
+      <c r="E2">
         <v>49</v>
       </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>308</v>
+        <v>577</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>308</v>
       </c>
       <c r="D3">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>308</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
+        <v>546.1</v>
+      </c>
+      <c r="C4">
         <v>307</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>42</v>
       </c>
-      <c r="D4">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>307</v>
-      </c>
-      <c r="G4">
-        <v>42</v>
-      </c>
-      <c r="H4">
+      <c r="E4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
+        <v>491.6</v>
+      </c>
+      <c r="C5">
         <v>306</v>
       </c>
-      <c r="C5">
-        <v>54</v>
-      </c>
       <c r="D5">
-        <v>39</v>
-      </c>
-      <c r="F5">
-        <v>306</v>
-      </c>
-      <c r="G5">
         <v>55</v>
       </c>
-      <c r="H5">
+      <c r="E5">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
+        <v>435.8</v>
+      </c>
+      <c r="C6">
         <v>305</v>
       </c>
-      <c r="C6">
-        <v>41</v>
-      </c>
       <c r="D6">
-        <v>5.5</v>
-      </c>
-      <c r="F6">
-        <v>305</v>
-      </c>
-      <c r="G6">
         <v>42</v>
       </c>
-      <c r="H6">
+      <c r="E6">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
+        <v>404.7</v>
+      </c>
+      <c r="C7">
         <v>304</v>
       </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
       <c r="D7">
-        <v>12</v>
-      </c>
-      <c r="F7">
-        <v>304</v>
-      </c>
-      <c r="G7">
         <v>45</v>
       </c>
-      <c r="H7">
+      <c r="E7">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>308</v>
+        <v>623.4</v>
       </c>
       <c r="C8">
+        <v>308</v>
+      </c>
+      <c r="D8">
         <v>26</v>
       </c>
-      <c r="D8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>308</v>
-      </c>
-      <c r="G8">
-        <v>26</v>
-      </c>
-      <c r="H8">
+      <c r="E8">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9">
-        <v>308</v>
+        <v>690.7</v>
       </c>
       <c r="C9">
+        <v>308</v>
+      </c>
+      <c r="D9">
         <v>53</v>
       </c>
-      <c r="D9">
-        <v>41</v>
-      </c>
-      <c r="F9">
-        <v>308</v>
-      </c>
-      <c r="G9">
-        <v>53</v>
-      </c>
-      <c r="H9">
+      <c r="E9">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
       <c r="F10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -769,6 +748,142 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>308</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>308</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>307</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>306</v>
+      </c>
+      <c r="C5">
+        <v>54</v>
+      </c>
+      <c r="D5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>305</v>
+      </c>
+      <c r="C6">
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>304</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>308</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>308</v>
+      </c>
+      <c r="C9">
+        <v>53</v>
+      </c>
+      <c r="D9">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
